--- a/specifications/features/v2.0/Anti_Scam_Feature_Backlog_V2.xlsx
+++ b/specifications/features/v2.0/Anti_Scam_Feature_Backlog_V2.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" r:id="Rd13765c581ac423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="2" r:id="R4696eeded13c427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work Packages" sheetId="3" r:id="Rcc0180c4e15541ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách tính năng" sheetId="4" r:id="R8362d6ce36ec427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP - P0" sheetId="5" r:id="R72851c0fa20d4957"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phân công team" sheetId="6" r:id="R6bf0a8b299624a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Future Scope" sheetId="7" r:id="R122814452d2845ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thay đổi V2" sheetId="8" r:id="R6e202a3e9a384262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng quan" sheetId="1" r:id="Rcd9922e74d5d48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="2" r:id="R3cb4966dc85f44fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Work Packages" sheetId="3" r:id="R085380a8c3194b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách tính năng" sheetId="4" r:id="R0dd1c8f9fe574179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVP - P0" sheetId="5" r:id="R4dc26729a48c4967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phân công team" sheetId="6" r:id="R27b62535ba18451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Future Scope" sheetId="7" r:id="R6bfef25b4ed54349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thay đổi V2" sheetId="8" r:id="R1e29c83289004956"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -671,7 +671,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25" t="str">
-        <x:v>M13 Platform Infrastructure + CI/CD trả về Khải. M04 → Kiên; M07 + M14 → Hùng. CI bắt đầu B0; CD MVP phải hoàn tất trước 20/10.</x:v>
+        <x:v>M13 Platform Infrastructure + CI/CD trả về Khải. M04 → Kiên; M07 + M14 → Hùng. CI bắt đầu W09; CD MVP phải hoàn tất trước 20/10.</x:v>
       </x:c>
       <x:c r="B10" s="25"/>
       <x:c r="C10" s="25"/>
@@ -3827,7 +3827,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a4be322d3b8415a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba26dc572cde463d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14847,7 +14847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c5e963acb4f4c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cacffea53d74848"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19371,7 +19371,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="18" t="str">
-        <x:v>CI P0: B0. CD/migration/image pipeline: xong trước 20/10. 27–30/10 chỉ freeze/regression/release rehearsal.</x:v>
+        <x:v>CI P0: W09. CD/migration/image pipeline: xong trước 20/10. 27–30/10 chỉ freeze/regression/release rehearsal.</x:v>
       </x:c>
       <x:c r="B8" s="18"/>
       <x:c r="C8" s="18"/>
@@ -20393,7 +20393,7 @@
         <x:v>CI timing</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
-        <x:v>K-WP11 bắt đầu B0</x:v>
+        <x:v>K-WP11 bắt đầu W09</x:v>
       </x:c>
       <x:c r="C6" s="23" t="str">
         <x:v>CI là enabling task; test đỏ phải chặn merge từ đầu.</x:v>
